--- a/output/full_scan/batch_seq1_2026-06-05.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-05.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1531</v>
+        <v>1342</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>835.711159458255</v>
+        <v>1049.412850627951</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13.15</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.35229537712281</v>
+        <v>75.0571512439281</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21.43981833929152</v>
+        <v>18.69720481758224</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.571115945825494</v>
+        <v>3.441285062795123</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0992429517640865</v>
+        <v>0.9670867470569542</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1231</v>
+        <v>1319</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>817.2065296286077</v>
+        <v>1045.677863931551</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>89</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>62.4229520389143</v>
+        <v>70.15170472944344</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>17.89069545058845</v>
+        <v>27.68546225707548</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.720652962860764</v>
+        <v>1.567786393155067</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.402503061827326</v>
+        <v>1.830398104666603</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1319</v>
+        <v>1531</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>810.6778639315506</v>
+        <v>1005.711159458255</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>13.15</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>70.15170466350509</v>
+        <v>63.35229545704296</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.68546229896087</v>
+        <v>21.43981846400044</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.567786393155067</v>
+        <v>2.571115945825494</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.830398104571198</v>
+        <v>0.09924295177362689</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>762.9903836002791</v>
+        <v>997.9903836002792</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>54.4</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.97183565899994</v>
+        <v>63.97183579638811</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>19.24534100786988</v>
+        <v>19.24534104084913</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.799038360027912</v>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
@@ -733,27 +733,27 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>759.4128506279512</v>
+        <v>959.8429780174504</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>104</v>
+        <v>17.45</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>75.05715115890425</v>
+        <v>68.76535157808533</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.69720478116582</v>
+        <v>20.4349648448128</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.441285062795123</v>
+        <v>0.9842978017450258</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.9670867470951036</v>
+        <v>0.1819892612888024</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1513</v>
+        <v>1231</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>737.5978306449674</v>
+        <v>957.2065296286077</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>170.5</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.99430469602361</v>
+        <v>62.42295222735437</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.19954493314177</v>
+        <v>17.89069566108567</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.25978306449674</v>
+        <v>1.720652962860764</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.075522780752357</v>
+        <v>0.402503061827326</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1533</v>
+        <v>1474</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>703.4684377081406</v>
+        <v>943.9955509723588</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>39.9</v>
+        <v>10.55</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>65.79564539331528</v>
+        <v>68.89374697448426</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>58.26607029503614</v>
+        <v>24.38185430463571</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.346843770814063</v>
+        <v>2.399555097235875</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.0742139902262484</v>
+        <v>0.083502186196541</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1338</v>
+        <v>1533</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>699.8429780174503</v>
+        <v>933.4684377081406</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>17.45</v>
+        <v>39.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.76535140562477</v>
+        <v>65.79564544150588</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20.4349648448128</v>
+        <v>58.26607024118473</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9842978017450258</v>
+        <v>1.346843770814063</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,11 +941,11 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1819892613174237</v>
+        <v>-0.0742139900449903</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>693.6880395937793</v>
+        <v>928.6880395937792</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>78.40000000000001</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.76069196767039</v>
+        <v>57.7606919937969</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>35.42208322870488</v>
+        <v>35.42208328509593</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.368803959377929</v>
@@ -988,37 +988,37 @@
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.9854289067647172</v>
+        <v>0.9854289065834624</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1503</v>
+        <v>1307</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>691.5901960346516</v>
+        <v>872.3327067800284</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>241.5</v>
+        <v>34.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.45436510358357</v>
+        <v>70.00966295629289</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>33.71364375597383</v>
+        <v>21.54114102745132</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.659019603465163</v>
+        <v>1.733270678002838</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>5.610775611004971</v>
+        <v>0.393945630291229</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1514</v>
+        <v>1303</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>686.2194739231131</v>
+        <v>867.0493248879361</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>135</v>
+        <v>104.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.36490288283078</v>
+        <v>60.64476465433614</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.4570071756262</v>
+        <v>26.88146454798746</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.621947392311312</v>
+        <v>0.7049324887936135</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.8418797415651</v>
+        <v>2.102239228747206</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1474</v>
+        <v>1503</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>683.9955509723587</v>
+        <v>861.5901960346516</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10.55</v>
+        <v>241.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.89374697448426</v>
+        <v>63.45436512487485</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24.38185389296374</v>
+        <v>33.71364371335255</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.399555097235875</v>
+        <v>3.659019603465163</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0835021861870007</v>
+        <v>5.610775611195766</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1218</v>
+        <v>1514</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>673.9887771249732</v>
+        <v>856.2194739231131</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>19.35</v>
+        <v>135</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.83562145032957</v>
+        <v>60.36490292124783</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.13892552167792</v>
+        <v>36.45700722658894</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.898877712497318</v>
+        <v>1.621947392311312</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1167041767870336</v>
+        <v>1.84187974146968</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1524</v>
+        <v>1513</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>659.3222340730306</v>
+        <v>852.5978306449674</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32.3</v>
+        <v>170.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.97412922422913</v>
+        <v>56.99430472086198</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.52298422920472</v>
+        <v>34.1995449806847</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4322234073030573</v>
+        <v>2.25978306449674</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.3499361073925402</v>
+        <v>2.07552278084778</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1563</v>
+        <v>1414</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>633.7148019095425</v>
+        <v>832.5485437818486</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>65.3</v>
+        <v>16.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>76.64061564828603</v>
+        <v>63.36126461755278</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>57.52928740495845</v>
+        <v>33.03646386201573</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.371480190954255</v>
+        <v>1.254854378184856</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.632103397693616</v>
+        <v>0.2483207313507784</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1568</v>
+        <v>1515</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>633.3918367367122</v>
+        <v>825</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>43.8</v>
+        <v>26.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.53102568355831</v>
+        <v>74.03777391846434</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>57.31430384460219</v>
+        <v>17.45407165020291</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3391836736712186</v>
+        <v>6.324457477353599</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.096563083049578</v>
+        <v>0.4278611231251743</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1515</v>
+        <v>1218</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>625</v>
+        <v>813.9887771249732</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>26.3</v>
+        <v>19.35</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>74.03777390666988</v>
+        <v>60.83562159748551</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.45407134729962</v>
+        <v>27.13892556992824</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6.324457477353599</v>
+        <v>1.898877712497318</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.4278611226577282</v>
+        <v>0.1167041767679541</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1447</v>
+        <v>1440</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>617.3836181824776</v>
+        <v>812.0517310606458</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6.41</v>
+        <v>14.25</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.12984002577016</v>
+        <v>63.20789441076003</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>43.20686847984562</v>
+        <v>34.95924584522625</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7383618182477536</v>
+        <v>1.705173106064578</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.08691164637925081</v>
+        <v>0.3837645174332613</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1530</v>
+        <v>1409</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>615.2099786442342</v>
+        <v>802.7585098249581</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>32.05</v>
+        <v>26.15</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.75330040071955</v>
+        <v>69.46903349804889</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>47.65743267462281</v>
+        <v>48.64876048909982</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5209978644234239</v>
+        <v>2.275850982495804</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2267798786696613</v>
+        <v>1.01685988652064</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1440</v>
+        <v>1456</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>612.0517310606458</v>
+        <v>791.2941584127844</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.25</v>
+        <v>14.45</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.20789440645541</v>
+        <v>64.29512081524472</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>34.95924572324552</v>
+        <v>16.33804526561763</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.705173106064578</v>
+        <v>2.129415841278445</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,11 +1577,11 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3837645173951011</v>
+        <v>0.1540562861084778</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>605.385468240898</v>
+        <v>775.385468240898</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>52.8</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.83031859905131</v>
+        <v>59.83031861733877</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>29.80825249858588</v>
+        <v>29.80825252190158</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.038546824089803</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.053501720851696</v>
+        <v>1.053501720918473</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1409</v>
+        <v>1423</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>602.7585098249581</v>
+        <v>769.3316003899754</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>26.15</v>
+        <v>43.75</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>69.4690334884618</v>
+        <v>68.63833802754735</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>48.6487604720735</v>
+        <v>32.63467237293234</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.275850982495804</v>
+        <v>0.4331600389975423</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.01685988652064</v>
+        <v>0.2772529096224218</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1303</v>
+        <v>1312</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>602.0493248879361</v>
+        <v>758.2205833092324</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>104.5</v>
+        <v>14.4</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>60.64476465048906</v>
+        <v>70.22480243846039</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.88146457311234</v>
+        <v>33.35668442131499</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7049324887936135</v>
+        <v>1.822058330923248</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.102239228613648</v>
+        <v>0.5492753832169905</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1456</v>
+        <v>1447</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>591.2941584127844</v>
+        <v>757.3836181824776</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>14.45</v>
+        <v>6.41</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>64.29512071525372</v>
+        <v>63.12984007085974</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.33804526561763</v>
+        <v>43.20686842960948</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.129415841278445</v>
+        <v>0.7383618182477536</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1540562861370981</v>
+        <v>0.08691164636780251</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1232</v>
+        <v>1432</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>578.6685898501963</v>
+        <v>736.0676229250341</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>149.5</v>
+        <v>17.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.84449823042667</v>
+        <v>61.97215789703484</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11.15840857429853</v>
+        <v>26.01067469943174</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.366858985019637</v>
+        <v>1.606762292503412</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2076066674047822</v>
+        <v>0.1316173523990242</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1104</v>
+        <v>1216</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>564.7962056798201</v>
+        <v>735.2274680191385</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>29.4</v>
+        <v>73.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>72.43629001312075</v>
+        <v>56.2431671065773</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>38.9239275518761</v>
+        <v>18.16299213638676</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.479620567982012</v>
+        <v>0.5227468019138565</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.2730370556432608</v>
+        <v>0.1313351738270253</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1312</v>
+        <v>1104</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>558.2205833092324</v>
+        <v>734.7962056798201</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>14.4</v>
+        <v>29.4</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>70.2248024120107</v>
+        <v>72.43629018735739</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33.35668440386593</v>
+        <v>38.92392759397839</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.822058330923248</v>
+        <v>1.479620567982012</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5492753832169905</v>
+        <v>0.273037055576481</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1110</v>
+        <v>1527</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>552.4046581783324</v>
+        <v>734.2724283959524</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>16</v>
+        <v>33.4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>68.48234855950083</v>
+        <v>59.42890027237224</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26.5066803674686</v>
+        <v>20.91436620358245</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.740465817833237</v>
+        <v>0.9272428395952406</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2508840860271765</v>
+        <v>0.0955990741490728</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1457</v>
+        <v>1236</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>550.6537971656861</v>
+        <v>728.0627484782493</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>74.36681233589772</v>
+        <v>59.72657129508758</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.77153796503772</v>
+        <v>18.79247191542844</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.065379716568611</v>
+        <v>0.8062748478249276</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2000339704938866</v>
+        <v>0.2050317391469829</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1455</v>
+        <v>1563</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>546.8381316748647</v>
+        <v>723.7148019095425</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.1</v>
+        <v>65.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>64.68520037917968</v>
+        <v>76.64061573577014</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>31.12590146842442</v>
+        <v>57.52928763403968</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.183813167486473</v>
+        <v>0.371480190954255</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1420170196084638</v>
+        <v>1.63210339759822</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1414</v>
+        <v>1568</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>542.5485437818486</v>
+        <v>723.3918367367122</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>16.9</v>
+        <v>43.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63.36126449463433</v>
+        <v>69.53102572438728</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>33.03646385802836</v>
+        <v>57.3143038337649</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.254854378184856</v>
+        <v>0.3391836736712186</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2483207313344285</v>
+        <v>1.096563083059117</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1339</v>
+        <v>1110</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>540.4663569983397</v>
+        <v>722.4046581783324</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>43.5</v>
+        <v>16</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.63507740357419</v>
+        <v>68.48234852074205</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.33212900690703</v>
+        <v>26.50668050104096</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5466356998339698</v>
+        <v>1.740465817833237</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2741274965495213</v>
+        <v>0.2508840861511921</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1423</v>
+        <v>1457</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>539.3316003899754</v>
+        <v>720.6537971656861</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>43.75</v>
+        <v>15.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>68.63833789710029</v>
+        <v>74.36681244924912</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>32.63467222448942</v>
+        <v>24.77153789988709</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4331600389975423</v>
+        <v>3.065379716568611</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2772529097178203</v>
+        <v>0.2000339704748081</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1324</v>
+        <v>1402</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>538.0180438786709</v>
+        <v>715.6626381171685</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10.7</v>
+        <v>27.55</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>58.27929896258507</v>
+        <v>58.15928729646072</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23.49735965065112</v>
+        <v>20.48193575255287</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.801804387867092</v>
+        <v>1.066263811716853</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0908940800844959</v>
+        <v>0.1927624264694978</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1307</v>
+        <v>1227</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>537.3327067800284</v>
+        <v>700.2447514439555</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>34.3</v>
+        <v>28.85</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>70.00966290845012</v>
+        <v>54.41980719535741</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.54114097608685</v>
+        <v>25.206516687058</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.733270678002838</v>
+        <v>1.524475144395546</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3939456301481357</v>
+        <v>0.0985873654428582</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1525</v>
+        <v>1560</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>537.2193681175083</v>
+        <v>699.4606937221853</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>66.5</v>
+        <v>698</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.39267700625344</v>
+        <v>58.9747242001268</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>30.49071009349742</v>
+        <v>34.6706090680546</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2219368117508257</v>
+        <v>0.446069372218525</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0887611020323346</v>
+        <v>-3.985517082703701</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1432</v>
+        <v>1232</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>531.0676229250341</v>
+        <v>693.6685898501963</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.2</v>
+        <v>149.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>61.9721577700651</v>
+        <v>58.84449864336303</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26.01067467587414</v>
+        <v>11.15840857438179</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.606762292503412</v>
+        <v>1.366858985019637</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1316173523894869</v>
+        <v>0.2076066669278005</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1527</v>
+        <v>1455</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>529.2724283959524</v>
+        <v>686.8381316748647</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>33.4</v>
+        <v>9.1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>59.42890008765603</v>
+        <v>64.68520029590994</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.91436613015086</v>
+        <v>31.12590164407368</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9272428395952406</v>
+        <v>1.183813167486473</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0955990740822954</v>
+        <v>0.1420170196637934</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1301</v>
+        <v>1324</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>525.1060144379121</v>
+        <v>678.0180438786709</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>48.9</v>
+        <v>10.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>52.45291363113837</v>
+        <v>58.27929900223971</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>26.07331827895748</v>
+        <v>23.4973597021204</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.010601443791209</v>
+        <v>0.801804387867092</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.6131837971266354</v>
+        <v>0.090894080094036</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1203</v>
+        <v>1444</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>523.2220620338633</v>
+        <v>674.7662737932819</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>42.85</v>
+        <v>6.85</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.15290715039464</v>
+        <v>61.47121131650852</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.25537524740429</v>
+        <v>37.82703130570293</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3222062033863255</v>
+        <v>1.476627379328189</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0238254229003702</v>
+        <v>0.1436970014288849</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>520.7130855339343</v>
+        <v>666.8579865142389</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>12.45</v>
+        <v>7.71</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>57.03432764069159</v>
+        <v>68.76687951502203</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.30451407036366</v>
+        <v>24.26212328009708</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.071308553393429</v>
+        <v>0.6857986514238883</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0472178643881928</v>
+        <v>0.09740500042337399</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1535</v>
+        <v>1301</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>517.0885338425669</v>
+        <v>665.1060144379121</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>51.1</v>
+        <v>48.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.90686217689706</v>
+        <v>52.45291366099922</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.80771370469572</v>
+        <v>26.07331823971459</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.708853384256696</v>
+        <v>1.010601443791209</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,51 +2743,51 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3343402321923284</v>
+        <v>0.6131837972315708</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1435</v>
+        <v>1524</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>515</v>
+        <v>659.3222340730306</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>12.85</v>
+        <v>32.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G44" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.81911646067804</v>
+        <v>59.97412942810038</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7.899472211174256</v>
+        <v>27.52298451848166</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.481734204897169</v>
+        <v>0.4322234073030573</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1142738568927359</v>
+        <v>0.3499361073639249</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1560</v>
+        <v>1535</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>514.4606937221852</v>
+        <v>657.0885338425669</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>698</v>
+        <v>51.1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>58.97472420350494</v>
+        <v>56.90686263841894</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>34.67060912918645</v>
+        <v>22.8077137825107</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.446069372218525</v>
+        <v>1.708853384256696</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-3.985517084420884</v>
+        <v>0.3343402317153447</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1444</v>
+        <v>1434</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>504.7662737932818</v>
+        <v>649.7502094417245</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>6.85</v>
+        <v>16.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>61.47121124984766</v>
+        <v>64.64783716382644</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>37.82703125123611</v>
+        <v>28.609368587433</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.476627379328189</v>
+        <v>0.9750209441724468</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1436970014460565</v>
+        <v>0.2253382781790072</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1416</v>
+        <v>1314</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>501.2514642245768</v>
+        <v>648.5260311102629</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11.7</v>
+        <v>8.09</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>66.87013904298763</v>
+        <v>62.73767719197303</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>36.72801468029116</v>
+        <v>12.58178826007699</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.125146422457681</v>
+        <v>1.352603111026291</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.08770980965589691</v>
+        <v>0.1606743502419546</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1341</v>
+        <v>1528</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>500.3367338300034</v>
+        <v>644.3077735965994</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>63.5</v>
+        <v>27.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>64.40325047875511</v>
+        <v>53.04051867841569</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.37553552471648</v>
+        <v>15.2392383109267</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5336733830003386</v>
+        <v>0.9307773596599364</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1671138141863436</v>
+        <v>0.3637069206790662</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1216</v>
+        <v>1540</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>500.2274680191385</v>
+        <v>643.5435774045818</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>73.8</v>
+        <v>22.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>56.24316706288113</v>
+        <v>61.59176359886931</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.16299199974026</v>
+        <v>28.50043189266672</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5227468019138565</v>
+        <v>1.854357740458185</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1313351741132217</v>
+        <v>0.2475934280556287</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>499.907719157076</v>
+        <v>641.2514642245768</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.97655513401608</v>
+        <v>66.87013924694713</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.25622608429837</v>
+        <v>36.72801472061374</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4907719157075952</v>
+        <v>1.125146422457681</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.332353250409387</v>
+        <v>0.08770980965589691</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1236</v>
+        <v>1341</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>498.0627484782493</v>
+        <v>640.3367338300034</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>25.5</v>
+        <v>63.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>59.72657119212814</v>
+        <v>64.40325052944937</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.79247191385077</v>
+        <v>16.3755354919675</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8062748478249276</v>
+        <v>0.5336733830003386</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.2050317392042225</v>
+        <v>0.1671138140718651</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1437</v>
+        <v>1419</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>487.82209406827</v>
+        <v>639.9077191570759</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>29.15</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>55.62784356212362</v>
+        <v>57.97655519716601</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>32.80657325423302</v>
+        <v>19.25622615704084</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2822094068269944</v>
+        <v>0.4907719157075952</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1808839193215824</v>
+        <v>0.3323532502758227</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1256</v>
+        <v>1532</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>487.7649037039042</v>
+        <v>635.5933365430075</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>181</v>
+        <v>22.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.61152078805015</v>
+        <v>71.63304783504513</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>39.47893327204748</v>
+        <v>30.36277832047939</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.276490370390425</v>
+        <v>1.05933365430075</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.087334539367216</v>
+        <v>0.2470366392873993</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1446</v>
+        <v>1304</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>484.7813652620542</v>
+        <v>633.3108242071391</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>16.6</v>
+        <v>13.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>65.00804632750047</v>
+        <v>52.54534124965102</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.477001390192</v>
+        <v>26.67510823692432</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.978136526205423</v>
+        <v>0.8310824207139109</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1593780501501601</v>
+        <v>0.2537609927739924</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1540</v>
+        <v>1443</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>473.5435774045819</v>
+        <v>629.9326453733776</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>22.6</v>
+        <v>27</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>61.59176352845675</v>
+        <v>63.5017746053072</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.50043179685298</v>
+        <v>13.0624871668789</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.854357740458185</v>
+        <v>2.49326453733776</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2475934279125334</v>
+        <v>-0.022456346915228</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1417</v>
+        <v>1446</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>473.1178262716963</v>
+        <v>624.7813652620542</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>16.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>55.65793708305448</v>
+        <v>65.00804661860256</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.1162548913792</v>
+        <v>26.47700169055308</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.811782627169636</v>
+        <v>0.978136526205423</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0611181170998207</v>
+        <v>0.1593780501787791</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1227</v>
+        <v>1460</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>470.2447514439555</v>
+        <v>616.30903610266</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>28.85</v>
+        <v>7.42</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.41980700313078</v>
+        <v>66.45165615016575</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.20651662137357</v>
+        <v>18.72496012639803</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.524475144395546</v>
+        <v>1.130903610265998</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0985873655000947</v>
+        <v>0.0558837972275886</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1467</v>
+        <v>1530</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>466.8579865142389</v>
+        <v>615.2099786442342</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>7.71</v>
+        <v>32.05</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>68.76687943752073</v>
+        <v>59.75330047311301</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.26212304460231</v>
+        <v>47.65743269424606</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6857986514238883</v>
+        <v>0.5209978644234239</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0974050003833087</v>
+        <v>0.2267798785551857</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1532</v>
+        <v>1417</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>465.5933365430075</v>
+        <v>613.1178262716963</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>22.4</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>71.63304774595497</v>
+        <v>55.65793731939632</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>30.36277805364311</v>
+        <v>27.11625494353482</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.05933365430075</v>
+        <v>1.811782627169636</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2470366392396984</v>
+        <v>0.0611181171055457</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1304</v>
+        <v>1340</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>463.3108242071391</v>
+        <v>604.1601700437843</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>13.4</v>
+        <v>5.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.54534124965102</v>
+        <v>59.28779434401715</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.67510824802929</v>
+        <v>25.52059956629087</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8310824207139109</v>
+        <v>0.916017004378439</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2537609927358321</v>
+        <v>0.0993314332590195</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>459.9326453733776</v>
+        <v>602.82209406827</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>27</v>
+        <v>29.15</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>63.50177442790346</v>
+        <v>55.62784385764485</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13.06248706322769</v>
+        <v>32.8065734142273</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.49326453733776</v>
+        <v>0.2822094068269944</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0224563466671956</v>
+        <v>0.1808839192452641</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1582</v>
+        <v>1464</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>454.3113616140771</v>
+        <v>592.0234783146689</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>103.5</v>
+        <v>10.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.75370810502813</v>
+        <v>62.83868602327333</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.83815057295957</v>
+        <v>24.35812158012325</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4311361614077126</v>
+        <v>1.20234783146689</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.9833794074444108</v>
+        <v>0.0768027444339848</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1464</v>
+        <v>1336</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>台翰</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>452.0234783146689</v>
+        <v>574.5439711730717</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10.6</v>
+        <v>14.35</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>62.83868576971809</v>
+        <v>64.45588280450995</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>24.35812149459264</v>
+        <v>25.7511633144232</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.20234783146689</v>
+        <v>0.9543971173071738</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.07680274444352329</v>
+        <v>0.1839518528342304</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1402</v>
+        <v>1103</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>450.6626381171685</v>
+        <v>571.1848208744213</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>27.55</v>
+        <v>13.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>58.15928733225663</v>
+        <v>58.87242903556375</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.4819356378401</v>
+        <v>19.21009143149199</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.066263811716853</v>
+        <v>1.118482087442143</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1927624263741031</v>
+        <v>0.0737290594990915</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1314</v>
+        <v>1219</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>448.5260311102629</v>
+        <v>565.8036146794616</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>8.09</v>
+        <v>13</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>62.73767718175201</v>
+        <v>52.08883296916505</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.58178826688247</v>
+        <v>35.34356639989176</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.352603111026291</v>
+        <v>1.580361467946163</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,11 +3909,11 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.160674350220967</v>
+        <v>0.09147706173652639</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>448.1379514885981</v>
+        <v>563.1379514885981</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>128.5</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>71.88181942420019</v>
+        <v>71.88181978604023</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.85562795316455</v>
+        <v>15.85562805461346</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1.313795148859808</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.2708198009040428</v>
+        <v>0.2708198004270556</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1460</v>
+        <v>1476</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>446.30903610266</v>
+        <v>562.7673226397533</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>7.42</v>
+        <v>355.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>66.45165610317977</v>
+        <v>57.26678100582817</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.72496001714605</v>
+        <v>16.31455310424586</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.130903610265998</v>
+        <v>0.776732263975331</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0558837972314047</v>
+        <v>3.04316113539797</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1521</v>
+        <v>1321</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>444.3850710198349</v>
+        <v>561.2510177309061</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>27.7</v>
+        <v>29.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>61.98329695040901</v>
+        <v>50.23722004727594</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.03630316312291</v>
+        <v>49.35539528406402</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.938507101983494</v>
+        <v>1.625101773090614</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.3003594759267501</v>
+        <v>0.1535226528124106</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, breakout_volume_confirm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1528</v>
+        <v>1454</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>444.3077735965994</v>
+        <v>558.6659958148931</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>27.8</v>
+        <v>13.05</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.04051866101715</v>
+        <v>49.9436382083793</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.23923838041038</v>
+        <v>25.91501155730071</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9307773596599364</v>
+        <v>0.3665995814893129</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3637069206504445</v>
+        <v>0.0330957316013432</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1340</v>
+        <v>1477</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>434.1601700437844</v>
+        <v>543.7449043511976</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>5.95</v>
+        <v>228</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>59.28779439241792</v>
+        <v>56.44443922600184</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>25.52059927482146</v>
+        <v>25.30723986179159</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.916017004378439</v>
+        <v>0.8744904351197689</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0993314332323082</v>
+        <v>2.394170690112221</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1219</v>
+        <v>1339</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>425.8036146794617</v>
+        <v>540.4663569983397</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13</v>
+        <v>43.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.08883281642304</v>
+        <v>57.63507763769415</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>35.34356633664503</v>
+        <v>29.33212912976348</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.580361467946163</v>
+        <v>0.5466356998339698</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0914770617556068</v>
+        <v>0.2741274966639958</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1476</v>
+        <v>1525</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>422.7673226397533</v>
+        <v>537.2193681175083</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>355.5</v>
+        <v>66.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>57.26678096634079</v>
+        <v>54.39267705759534</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.31455304926478</v>
+        <v>30.4907100421764</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.776732263975331</v>
+        <v>0.2219368117508257</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>3.043161131868279</v>
+        <v>0.0887611019941838</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1321</v>
+        <v>1459</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>421.2510177309061</v>
+        <v>534.2211746809954</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>29.7</v>
+        <v>11.75</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>50.2372198825977</v>
+        <v>50.97006807913826</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49.35539514587438</v>
+        <v>20.83974383924484</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.625101773090614</v>
+        <v>0.9221174680995424</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1535226528505671</v>
+        <v>0.0018947460066968</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, breakout_volume_confirm</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1454</v>
+        <v>1313</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>418.6659958148931</v>
+        <v>531.7488045912664</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>13.05</v>
+        <v>11.25</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.94363796646821</v>
+        <v>52.84405833742735</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.91501155730071</v>
+        <v>20.47722669183227</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3665995814893129</v>
+        <v>1.17488045912665</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0330957318016772</v>
+        <v>0.149675311082526</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1217</v>
+        <v>1203</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>405.1129386824059</v>
+        <v>523.2220620338633</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>9.92</v>
+        <v>42.85</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>58.47336631419003</v>
+        <v>50.15290722890912</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>34.34342686130195</v>
+        <v>20.25537521349444</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.011293868240592</v>
+        <v>0.3222062033863255</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.07757795687879911</v>
+        <v>0.0238254228431341</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1434</v>
+        <v>1465</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>404.7502094417245</v>
+        <v>520.7130855339343</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>16.6</v>
+        <v>12.45</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>64.64783709085434</v>
+        <v>57.03432776722329</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28.6093685594541</v>
+        <v>24.30451415470177</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9750209441724468</v>
+        <v>2.071308553393429</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.2253382781885499</v>
+        <v>0.0472178643691115</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1336</v>
+        <v>1217</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台翰</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>404.5439711730717</v>
+        <v>520.1129386824059</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>14.35</v>
+        <v>9.92</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>64.45588275509544</v>
+        <v>58.47336631419003</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25.75116275168716</v>
+        <v>34.34342683771377</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9543971173071738</v>
+        <v>1.011293868240592</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,48 +4545,48 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1839518527483729</v>
+        <v>0.0775779568692597</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1477</v>
+        <v>1435</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>403.7449043511977</v>
+        <v>515</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>228</v>
+        <v>12.85</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>56.44443932964177</v>
+        <v>49.81911394375345</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>25.3072397528165</v>
+        <v>7.899471595263902</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8744904351197689</v>
+        <v>8.481734204897169</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>2.394170687154917</v>
+        <v>0.1142739056632304</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1539</v>
+        <v>1234</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>黑松</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>403.7040578485076</v>
+        <v>503.733783543173</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>16.35</v>
+        <v>35.15</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>55.76665925784262</v>
+        <v>58.98937514351862</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>29.45182236929186</v>
+        <v>22.43927432716226</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8704057848507546</v>
+        <v>0.8733783543172989</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.109213128123451</v>
+        <v>0.1954052581967122</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1522</v>
+        <v>1309</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>398.8985561758744</v>
+        <v>502.4696386011856</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>32.1</v>
+        <v>16.35</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>52.37106879711585</v>
+        <v>46.73423305866746</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25.93206452683698</v>
+        <v>15.04194249416346</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3898556175874434</v>
+        <v>0.7469638601185662</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.4306635019832044</v>
+        <v>0.2624489161609772</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1313</v>
+        <v>1201</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>391.7488045912665</v>
+        <v>497.4422509079584</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>11.25</v>
+        <v>12.45</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.84405830956199</v>
+        <v>51.92699277604488</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.47722669368167</v>
+        <v>42.00850525599064</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.17488045912665</v>
+        <v>0.7442250907958353</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1496753110729866</v>
+        <v>0.0949704973610252</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1234</v>
+        <v>1305</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>黑松</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>388.733783543173</v>
+        <v>494.5483010501578</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>35.15</v>
+        <v>13.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>58.98937497680669</v>
+        <v>49.57547813744296</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22.43927418066669</v>
+        <v>16.59169715964785</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8733783543172989</v>
+        <v>0.9548301050157794</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1954052582348734</v>
+        <v>0.2208608506362133</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>376.9270809280969</v>
+        <v>493.5812291500717</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>22.4</v>
+        <v>11.45</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.20886282463822</v>
+        <v>52.57166743064878</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3.510849736422776</v>
+        <v>17.27914470103381</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.69270809280969</v>
+        <v>0.8581229150071621</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0295054938235133</v>
+        <v>0.1926816106826012</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1309</v>
+        <v>1438</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>362.4696386011856</v>
+        <v>490.989158406822</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>16.35</v>
+        <v>20.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.73423305052706</v>
+        <v>40.57674453700624</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15.04194248958987</v>
+        <v>37.33587473046114</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7469638601185662</v>
+        <v>2.098915840682201</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2624489161132796</v>
+        <v>0.2730521464948703</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>357.4422509079583</v>
+        <v>487.7649037039042</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>12.45</v>
+        <v>181</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.92699243626014</v>
+        <v>46.61152081746541</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>42.00850515984246</v>
+        <v>39.47893314658638</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7442250907958353</v>
+        <v>2.276490370390425</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0949704974373439</v>
+        <v>-1.087334539176419</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>355.2288954669417</v>
+        <v>486.6925279475517</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>851</v>
+        <v>10.45</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.04343476249888</v>
+        <v>53.7404008956844</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.96314392397437</v>
+        <v>30.51758481297552</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.522889546694171</v>
+        <v>1.169252794755169</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>6.391610820643527</v>
+        <v>0.1059650375135741</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1517</v>
+        <v>1452</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>346.6925279475517</v>
+        <v>482.9875395450831</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>10.45</v>
+        <v>11.05</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.74040076803517</v>
+        <v>56.86134649333089</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30.51758467133842</v>
+        <v>27.47721731931266</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.169252794755169</v>
+        <v>0.7987539545083063</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1059650375040347</v>
+        <v>0.0852067198402445</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1452</v>
+        <v>1229</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>342.9875395450831</v>
+        <v>482.9630082143465</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>11.05</v>
+        <v>42</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>56.86134635699097</v>
+        <v>54.73080868931466</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>27.47721729960258</v>
+        <v>32.74845658179789</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7987539545083063</v>
+        <v>0.7963008214346482</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.08520671983070439</v>
+        <v>0.5626337709652673</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1229</v>
+        <v>1337</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>再生-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>342.9630082143465</v>
+        <v>480.943762401051</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>42</v>
+        <v>5.06</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>54.7308087059173</v>
+        <v>52.20426596657239</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>32.74845651341838</v>
+        <v>29.60268595198022</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7963008214346482</v>
+        <v>0.5943762401050976</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.5626337708698612</v>
+        <v>0.070344310774372</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>341.0417862194695</v>
+        <v>475.3380912259834</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>119</v>
+        <v>11.95</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>29.54152504075735</v>
+        <v>45.88260729585895</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>36.09638257238552</v>
+        <v>29.62562483277543</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.604178621946957</v>
+        <v>0.533809122598338</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-2.172994930259507</v>
+        <v>0.0347759596178001</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1337</v>
+        <v>1449</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>再生-KY</t>
+          <t>佳和</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>340.943762401051</v>
+        <v>455.0810492649565</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>5.06</v>
+        <v>13.55</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.20426588607595</v>
+        <v>55.25296522459902</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>29.60268570375102</v>
+        <v>19.01734742862857</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5943762401050976</v>
+        <v>0.5081049264956433</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.07034431076864869</v>
+        <v>0.1551664681828395</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1459</v>
+        <v>1529</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>329.2211746809954</v>
+        <v>454.4633272570153</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>11.75</v>
+        <v>23.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>50.97006775219866</v>
+        <v>54.24892774884292</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.83974396319288</v>
+        <v>23.83002487526739</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9221174680995424</v>
+        <v>0.9463327257015312</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0018947460448553</v>
+        <v>0.3785273882701124</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1529</v>
+        <v>1582</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>314.4633272570153</v>
+        <v>454.3113616140771</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>23.05</v>
+        <v>103.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>54.24892765392094</v>
+        <v>47.75370810776369</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23.83002473656637</v>
+        <v>27.83815091416579</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9463327257015312</v>
+        <v>0.4311361614077126</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.3785273882128711</v>
+        <v>-0.983379407005602</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1536</v>
+        <v>1526</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>301.3749075130518</v>
+        <v>451.4727286777954</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>50.5</v>
+        <v>15.25</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.22221982073916</v>
+        <v>50.3891275135848</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12.29446181784616</v>
+        <v>25.00910864706363</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.637490751305185</v>
+        <v>0.6472728677795441</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0119849462127971</v>
+        <v>0.1811727056404388</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1102</v>
+        <v>1521</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>301.2920439372431</v>
+        <v>444.3850710198349</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>34.4</v>
+        <v>27.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.7372131300193</v>
+        <v>61.9832971112468</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.66101885643789</v>
+        <v>22.03630308709885</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6292043937243105</v>
+        <v>0.938507101983494</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0835078017507577</v>
+        <v>0.3003594759362856</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1569</v>
+        <v>1418</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>300.7198769033344</v>
+        <v>443.0086076916793</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>51.1</v>
+        <v>18.65</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.16919203428051</v>
+        <v>51.91576515530655</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.94241901211033</v>
+        <v>18.70817286948615</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5719876903334339</v>
+        <v>0.3008607691679323</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0450552158444154</v>
+        <v>0.0984997882609162</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1516</v>
+        <v>1215</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>297.0803612621212</v>
+        <v>431.0417862194696</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.05286379017607</v>
+        <v>29.54152504646562</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.17394329983865</v>
+        <v>36.09638262560669</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2080361262121267</v>
+        <v>1.604178621946957</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0062970926697292</v>
+        <v>-2.172994930240408</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1103</v>
+        <v>1436</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>291.1848208744214</v>
+        <v>427.0457849102143</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>13.6</v>
+        <v>45.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>58.8724289299148</v>
+        <v>39.31272443995711</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.21009139529124</v>
+        <v>41.27452823260143</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.118482087442143</v>
+        <v>0.7045784910214309</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0737290595086318</v>
+        <v>0.3422801526672139</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1323</v>
+        <v>1475</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>288.7796380966265</v>
+        <v>424.1399308378805</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>20.15</v>
+        <v>25.95</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.25935921805009</v>
+        <v>45.71644328250507</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.92732371669388</v>
+        <v>36.67738010226967</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.8779638096626542</v>
+        <v>0.4139930837880465</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0686622343490033</v>
+        <v>0.1692752597081014</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1471</v>
+        <v>1102</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>288.5812291500716</v>
+        <v>416.2920439372431</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>11.45</v>
+        <v>34.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,49 +5746,49 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.57166740245212</v>
+        <v>50.7372130615279</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.27914457824937</v>
+        <v>13.66101888102519</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8581229150071621</v>
+        <v>0.6292043937243105</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1926816106902313</v>
+        <v>0.08350780176029959</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1108</v>
+        <v>1310</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>288.2596670982704</v>
+        <v>413.0666312745616</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>13.8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.09406310002239</v>
+        <v>53.77361159062955</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>48.32328938197449</v>
+        <v>32.19795659017607</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.325966709827036</v>
+        <v>1.30666312745616</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.06507346994355639</v>
+        <v>0.2144221381866589</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1436</v>
+        <v>1516</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>287.0457849102143</v>
+        <v>412.0803612621213</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>45.7</v>
+        <v>21</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.31272430829802</v>
+        <v>48.05286368295617</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>41.27452752718454</v>
+        <v>18.17394327508462</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7045784910214309</v>
+        <v>0.2080361262121267</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.3422801516178451</v>
+        <v>0.0062970926983493</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>285.989158406822</v>
+        <v>411.4404260045106</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>20.6</v>
+        <v>27.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.57674424861752</v>
+        <v>55.89093144457937</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>37.33587456311768</v>
+        <v>17.17642710231876</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.098915840682201</v>
+        <v>1.644042600451067</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.273052146618888</v>
+        <v>0.2230233059832752</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1449</v>
+        <v>1539</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>佳和</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>285.0810492649564</v>
+        <v>403.7040578485076</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>13.55</v>
+        <v>16.35</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>55.25296512210348</v>
+        <v>55.7666594149022</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.01734736583023</v>
+        <v>29.45182267119637</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5081049264956433</v>
+        <v>0.8704057848507546</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1551664681732999</v>
+        <v>0.1092131281902304</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>284.1399308378805</v>
+        <v>402.1037377287138</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>25.95</v>
+        <v>21.3</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.71644261123188</v>
+        <v>51.88028360013674</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>36.67738010091891</v>
+        <v>31.17533185583263</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4139930837880465</v>
+        <v>0.7103737728713855</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1692752597367209</v>
+        <v>0.2378201982158805</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>281.4727286777954</v>
+        <v>398.8985561758744</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15.25</v>
+        <v>32.1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>50.38912745246028</v>
+        <v>52.37106907674526</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>25.00910861316027</v>
+        <v>25.93206464978279</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6472728677795441</v>
+        <v>0.3898556175874434</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1811727056022793</v>
+        <v>0.4306635019736653</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1220</v>
+        <v>1466</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>270.3380912259834</v>
+        <v>397.8171948126093</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>11.95</v>
+        <v>14.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.88260703518083</v>
+        <v>43.34087697068304</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>29.62562479949997</v>
+        <v>22.40348340557577</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.533809122598338</v>
+        <v>0.7817194812609281</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0347759596273393</v>
+        <v>0.0877632596138703</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1466</v>
+        <v>1308</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>257.8171948126093</v>
+        <v>382.2759961817927</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>14.5</v>
+        <v>13.85</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.34087679490034</v>
+        <v>49.65443876829803</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>22.40348340557577</v>
+        <v>19.81557613173945</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7817194812609281</v>
+        <v>0.7275996181792709</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0877632595947917</v>
+        <v>0.1990610161165922</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1213</v>
+        <v>1470</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>257.7761218303005</v>
+        <v>376.9270809280969</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>8.43</v>
+        <v>22.4</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>51.15348978312667</v>
+        <v>52.20886282463822</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.89617136254037</v>
+        <v>3.510849736739172</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.277612183030054</v>
+        <v>0.69270809280969</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2826497444737942</v>
+        <v>0.0295054938807486</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1506</v>
+        <v>1213</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>257.5660791769055</v>
+        <v>372.7761218303006</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10.2</v>
+        <v>8.43</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45.04809877280081</v>
+        <v>51.15348978819465</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20.93894452254479</v>
+        <v>12.89617137131712</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.25660791769055</v>
+        <v>1.277612183030054</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,11 +6294,11 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0239098693514691</v>
+        <v>-0.2826497444356352</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>252.9005076504586</v>
+        <v>367.9005076504586</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>9.5</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.85866417295529</v>
+        <v>50.85866421040805</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7.133258877380176</v>
+        <v>7.133258882312487</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.7900507650458561</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0204533158889855</v>
+        <v>0.0204533158985241</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1445</v>
+        <v>1541</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>250.2747426909308</v>
+        <v>361.7659636622085</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>11.65</v>
+        <v>22.35</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>41.9957397019631</v>
+        <v>52.56198928896638</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.17305993173538</v>
+        <v>16.67713296458468</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5274742690930787</v>
+        <v>1.176596366220852</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0352044168056065</v>
+        <v>0.3303440786912658</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1463</v>
+        <v>1519</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>249.8401842180995</v>
+        <v>355.2288954669417</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17.7</v>
+        <v>851</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.6979657629335</v>
+        <v>48.04343482901243</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>9.384309126701851</v>
+        <v>14.96314391163632</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.484018421809946</v>
+        <v>1.522889546694171</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0056766163052529</v>
+        <v>6.391610820643527</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1439</v>
+        <v>1506</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>248.131326569306</v>
+        <v>347.5660791769055</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>25.5</v>
+        <v>10.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>49.67330429818384</v>
+        <v>45.04809917034293</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3.774725226040907</v>
+        <v>20.9389445671307</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.313132656930594</v>
+        <v>1.25660791769055</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0358700893023121</v>
+        <v>0.0239098693228501</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1468</v>
+        <v>1439</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>247.8031879938105</v>
+        <v>338.1313265693059</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>12.05</v>
+        <v>25.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45.94290507197125</v>
+        <v>49.67330432205683</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.638134645663584</v>
+        <v>3.774725168286554</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.280318799381046</v>
+        <v>0.313132656930594</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0104253595327459</v>
+        <v>0.0358700892927741</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1541</v>
+        <v>1558</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>246.7659636622085</v>
+        <v>331.3176900363628</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>22.35</v>
+        <v>91.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>52.56198926680962</v>
+        <v>53.40238658163014</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.67713294640201</v>
+        <v>16.65794142669728</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.176596366220852</v>
+        <v>0.6317690036362821</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.3303440784909329</v>
+        <v>0.2129164927440088</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1308</v>
+        <v>1109</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>242.2759961817927</v>
+        <v>323.0530313136658</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>13.85</v>
+        <v>14.85</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>49.65443884147764</v>
+        <v>48.46464906517478</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19.81557598394426</v>
+        <v>37.04926844357279</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7275996181792709</v>
+        <v>0.3053031313665848</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1990610160021146</v>
+        <v>0.0512105737080163</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1442</v>
+        <v>1101</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>241.4404260045107</v>
+        <v>314.9880957251371</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>27.3</v>
+        <v>24.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,49 +6700,49 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>55.89093171947133</v>
+        <v>49.75929225331983</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17.17642664004518</v>
+        <v>14.51856127369885</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.644042600451067</v>
+        <v>0.9988095725137084</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M118" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.2230233057733982</v>
+        <v>0.0458931368603616</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1558</v>
+        <v>1316</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>241.3176900363628</v>
+        <v>308.9274916479081</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>91.8</v>
+        <v>10.6</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>53.40238638710415</v>
+        <v>45.38675740076632</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.65794142669728</v>
+        <v>19.90517998362249</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.6317690036362821</v>
+        <v>0.8927491647908127</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2129164928775658</v>
+        <v>0.077123232732282</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1315</v>
+        <v>1536</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>240.809643013277</v>
+        <v>301.3749075130518</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>61.5</v>
+        <v>50.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>46.63008963314869</v>
+        <v>46.2222200084067</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.51633141410684</v>
+        <v>12.29446185423988</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5809643013276961</v>
+        <v>0.637490751305185</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1669217608741017</v>
+        <v>-0.0119849460220045</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1418</v>
+        <v>1569</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>238.0086076916793</v>
+        <v>300.7198769033344</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>18.65</v>
+        <v>51.1</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>51.91576503275384</v>
+        <v>43.16919214056141</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.70817294630845</v>
+        <v>11.94241905710111</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3008607691679323</v>
+        <v>0.5719876903334339</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.09849978834677039</v>
+        <v>0.045055216226004</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1305</v>
+        <v>1472</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>234.5483010501578</v>
+        <v>300</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>13.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.57547806601826</v>
+        <v>51.48771384090414</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>16.5916971858945</v>
+        <v>14.99174514570448</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.9548301050157794</v>
+        <v>5.779657099814255</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.2208608505789754</v>
+        <v>1.398121659865718</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1101</v>
+        <v>1323</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>219.9880957251371</v>
+        <v>288.7796380966265</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>24.4</v>
+        <v>20.15</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>49.75929223340269</v>
+        <v>49.25935930042609</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>14.51856127369884</v>
+        <v>13.92732416027587</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.9988095725137084</v>
+        <v>0.8779638096626542</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0458931368794417</v>
+        <v>0.0686622343585462</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1310</v>
+        <v>1108</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>213.0666312745616</v>
+        <v>288.2596670982704</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>53.77361161269499</v>
+        <v>42.09406334426246</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>32.19795665405974</v>
+        <v>48.32328948143402</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.30666312745616</v>
+        <v>2.325966709827036</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.2144221381313285</v>
+        <v>0.0650734698958591</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1472</v>
+        <v>1451</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>210</v>
+        <v>284.4059234603521</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>51.48771383196984</v>
+        <v>48.77312155706153</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>14.99174507868745</v>
+        <v>16.68981575887189</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>5.779657099814255</v>
+        <v>0.4405923460352167</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>1.39812165984665</v>
+        <v>0.0607369781398791</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1109</v>
+        <v>1225</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>208.0530313136658</v>
+        <v>282.4088164550162</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>14.85</v>
+        <v>29.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>48.46464869245315</v>
+        <v>42.04245634026367</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>37.04926817085164</v>
+        <v>13.28161001880377</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.3053031313665848</v>
+        <v>0.7408816455016227</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.051210573727097</v>
+        <v>0.0868699483770795</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1473</v>
+        <v>1512</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>197.1037377287139</v>
+        <v>256.3699019539039</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>21.3</v>
+        <v>7.08</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>51.88028345600014</v>
+        <v>49.65383075355058</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>31.17533167549438</v>
+        <v>13.23604586618588</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.7103737728713855</v>
+        <v>1.136990195390394</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.2378201982635798</v>
+        <v>0.0417477077283322</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1233</v>
+        <v>1445</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>177.3955476839271</v>
+        <v>250.2747426909308</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>27.7</v>
+        <v>11.65</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>32.8584692583814</v>
+        <v>41.99573974205682</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>24.8667570177204</v>
+        <v>10.17305999906682</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.2395547683927072</v>
+        <v>0.5274742690930787</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0452542405303105</v>
+        <v>0.0352044168533051</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1451</v>
+        <v>1463</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>169.4059234603522</v>
+        <v>249.8401842180995</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>16.8</v>
+        <v>17.7</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>48.77312127037935</v>
+        <v>43.69796630284021</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>16.68981572130653</v>
+        <v>9.384309245591837</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.4405923460352167</v>
+        <v>1.484018421809946</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.060736978187579</v>
+        <v>-0.0056766163147938</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1316</v>
+        <v>1468</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>168.9274916479081</v>
+        <v>247.8031879938105</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>10.6</v>
+        <v>12.05</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>45.38675740076632</v>
+        <v>45.94290553222304</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>19.90517980836275</v>
+        <v>8.638134808211159</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.8927491647908127</v>
+        <v>1.280318799381046</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.077123232684584</v>
+        <v>0.0104253595709052</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1325</v>
+        <v>1315</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>167.5319385277128</v>
+        <v>240.809643013277</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>26.65</v>
+        <v>61.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>47.59530112939808</v>
+        <v>46.6300897861323</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>16.81648093116612</v>
+        <v>18.51633143965876</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.7531938527712768</v>
+        <v>0.5809643013276961</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0128296754122374</v>
+        <v>0.1669217607405478</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1225</v>
+        <v>1441</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>167.4088164550162</v>
+        <v>212.8496316781936</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>42.04245634026367</v>
+        <v>44.67582234743991</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>13.28161001880377</v>
+        <v>11.90435303303957</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.7408816455016227</v>
+        <v>0.7849631678193543</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0868699483770795</v>
+        <v>0.0542901766734777</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1235</v>
+        <v>1453</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>興泰</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>164.6783608372428</v>
+        <v>211.3120937722974</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>38.7</v>
+        <v>11.4</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>41.91958802277181</v>
+        <v>47.28708496988055</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>13.33204636114079</v>
+        <v>18.94937540999121</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.4678360837242851</v>
+        <v>0.6312093772297396</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.0504268715379876</v>
+        <v>0.0586397486659922</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>1512</v>
+        <v>1538</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>116.369901953904</v>
+        <v>206.6330286569747</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>7.08</v>
+        <v>12</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>49.65383357579982</v>
+        <v>51.90285831139617</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>13.23604473308854</v>
+        <v>5.172022685621049</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.136990195390394</v>
+        <v>0.1633028656974708</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.0417477065454061</v>
+        <v>0.3905624930270824</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>1441</v>
+        <v>1233</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>97.84963167819356</v>
+        <v>177.3955476839271</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>9.5</v>
+        <v>27.7</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>44.67582216134279</v>
+        <v>32.85846963696312</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>11.90435305515262</v>
+        <v>24.86675736271386</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.7849631678193543</v>
+        <v>0.2395547683927072</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.0542901767211774</v>
+        <v>-0.045254240644786</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>1410</v>
+        <v>1325</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>96.7859608349647</v>
+        <v>167.5319385277128</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>25.85</v>
+        <v>26.65</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>38.33420604214632</v>
+        <v>47.5953012844713</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.74334923275887</v>
+        <v>16.81648093199739</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.6785960834964704</v>
+        <v>0.7531938527712768</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.1404978943847539</v>
+        <v>-0.0128296754408571</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>1453</v>
+        <v>1235</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>興泰</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>96.3120937722974</v>
+        <v>164.6783608372428</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>11.4</v>
+        <v>38.7</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>47.28708455598387</v>
+        <v>41.91958834010462</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>18.94937524875335</v>
+        <v>13.33204634016639</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.6312093772297396</v>
+        <v>0.4678360837242851</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.058639748694613</v>
+        <v>0.0504268705840147</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>1538</v>
+        <v>1410</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>91.6330286569747</v>
+        <v>96.7859608349647</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>12</v>
+        <v>25.85</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>51.90285831139617</v>
+        <v>38.3342060803622</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>5.17202268499318</v>
+        <v>12.74334927822086</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.1633028656974708</v>
+        <v>0.6785960834964704</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.3905624930270824</v>
+        <v>0.1404978942988972</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
